--- a/public/report_templates/caja/reportes/vchCobranzaVirtual.xlsx
+++ b/public/report_templates/caja/reportes/vchCobranzaVirtual.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\CredipymeApp\public\report_templates\caja\reportes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\CredypymeApp\public\report_templates\caja\reportes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415418E4-28F9-4A35-9BCC-B40736EF5A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC27520-8DE2-467C-836D-B528C7BCC73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AFC928B-410F-4A53-A090-F50511B27738}"/>
   </bookViews>
@@ -249,12 +249,6 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -262,22 +256,10 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
@@ -285,11 +267,29 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -315,59 +315,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>619413</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>26008</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>503870</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>11645</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="42" name="Gráfico 41">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{921E6C55-7958-4038-98D7-02DDC260BB03}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="619413" y="194527"/>
-          <a:ext cx="1642919" cy="395945"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -395,13 +342,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -424,22 +371,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>67220</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>158482</xdr:rowOff>
+      <xdr:colOff>747347</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>131884</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1056062</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>178394</xdr:rowOff>
+      <xdr:colOff>388327</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>73802</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Gráfico 45">
+        <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F3743F9-C424-40E3-A960-9ACB4D1A3F6C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65F4B5C1-7D11-95CF-C13D-C07E97BCD731}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -448,13 +395,10 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId6"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -464,8 +408,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="67220" y="883847"/>
-          <a:ext cx="2747304" cy="2745528"/>
+          <a:off x="747347" y="131884"/>
+          <a:ext cx="1384788" cy="520745"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -478,9 +422,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -518,7 +462,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -624,7 +568,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -766,7 +710,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -787,42 +731,42 @@
     <row r="2" spans="1:6" ht="32.25" customHeight="1"/>
     <row r="3" spans="1:6" ht="11.25" customHeight="1"/>
     <row r="4" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
     </row>
     <row r="5" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
     </row>
     <row r="6" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
     </row>
     <row r="7" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
     </row>
     <row r="8" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="13"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="6"/>
     </row>
     <row r="9" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B9" s="6"/>
@@ -830,62 +774,62 @@
       <c r="F9" s="1"/>
     </row>
     <row r="10" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="22"/>
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="15"/>
+      <c r="C11" s="22"/>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
     </row>
     <row r="13" spans="1:6" ht="11.25" customHeight="1">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="16">
+      <c r="B13" s="18"/>
+      <c r="C13" s="11">
         <v>0</v>
       </c>
       <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:6" ht="11.25" customHeight="1">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="16"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="11"/>
     </row>
     <row r="15" spans="1:6" ht="11.25" customHeight="1">
-      <c r="A15" s="22"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="16"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="11"/>
     </row>
     <row r="16" spans="1:6" ht="11.25" customHeight="1">
-      <c r="A16" s="22"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="16"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="11"/>
     </row>
     <row r="17" spans="1:3" ht="19.5" customHeight="1">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="8"/>
+      <c r="B17" s="19"/>
       <c r="C17" s="7">
         <v>0</v>
       </c>
@@ -896,63 +840,63 @@
       <c r="C18" s="6"/>
     </row>
     <row r="19" spans="1:3" ht="12.75" customHeight="1">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="18" t="s">
+      <c r="B19" s="20"/>
+      <c r="C19" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="12.75" customHeight="1">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="16">
+      <c r="B20" s="20"/>
+      <c r="C20" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="4.5" customHeight="1">
-      <c r="A21" s="13"/>
+      <c r="A21" s="10"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
     </row>
     <row r="22" spans="1:3" ht="16.5">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
     </row>
     <row r="23" spans="1:3" ht="16.5">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
     </row>
     <row r="24" spans="1:3" ht="16.5">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="23" t="s">
+      <c r="A26" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="13">

--- a/public/report_templates/caja/reportes/vchCobranzaVirtual.xlsx
+++ b/public/report_templates/caja/reportes/vchCobranzaVirtual.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\CredypymeApp\public\report_templates\caja\reportes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS\CredypymeApp\public\report_templates\caja\reportes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC27520-8DE2-467C-836D-B528C7BCC73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C658AE8-FBC8-4FDE-B807-53241D715364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AFC928B-410F-4A53-A090-F50511B27738}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{9AFC928B-410F-4A53-A090-F50511B27738}"/>
   </bookViews>
   <sheets>
     <sheet name="vchCobranza" sheetId="1" r:id="rId1"/>
@@ -371,22 +371,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>747347</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>131884</xdr:rowOff>
+      <xdr:colOff>776657</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>21983</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>388327</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>73802</xdr:rowOff>
+      <xdr:colOff>271096</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>388731</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2">
+        <xdr:cNvPr id="6" name="Imagen 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65F4B5C1-7D11-95CF-C13D-C07E97BCD731}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FA86809-19CA-6BA6-E1BA-B6D92DC602DC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -408,8 +408,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="747347" y="131884"/>
-          <a:ext cx="1384788" cy="520745"/>
+          <a:off x="776657" y="190502"/>
+          <a:ext cx="1252901" cy="366748"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -862,17 +862,17 @@
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
     </row>
-    <row r="22" spans="1:3" ht="16.5">
+    <row r="22" spans="1:3">
       <c r="A22" s="13"/>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
     </row>
-    <row r="23" spans="1:3" ht="16.5">
+    <row r="23" spans="1:3">
       <c r="A23" s="13"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
     </row>
-    <row r="24" spans="1:3" ht="16.5">
+    <row r="24" spans="1:3">
       <c r="A24" s="13"/>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
